--- a/INSTANCES/instances_xlsx/A_MTN_5/262FL_10A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/262FL_10A_5.xlsx
@@ -8654,7 +8654,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -8722,7 +8722,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
